--- a/Tagihan/2026/Juli/Pak Julian.xlsx
+++ b/Tagihan/2026/Juli/Pak Julian.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F3450DF-A1E5-4C5A-995A-EAC8D9D04D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEB2D70-39D0-4594-B8D4-AFB2B63BB6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>NO.</t>
   </si>
@@ -217,6 +216,18 @@
   <si>
     <t>Meter</t>
   </si>
+  <si>
+    <t xml:space="preserve">Tambahan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braket  TV  32 in - 50in </t>
+  </si>
+  <si>
+    <t>Paket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paket Ezvis H6C PRO 2K Memori 32 GB </t>
+  </si>
 </sst>
 </file>
 
@@ -225,7 +236,7 @@
   <numFmts count="1">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +322,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -320,7 +338,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -597,11 +615,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -684,6 +733,18 @@
     <xf numFmtId="42" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -748,17 +809,26 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -832,14 +902,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>154781</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2320131</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>79851</xdr:rowOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>79850</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1173,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:N47"/>
+  <dimension ref="B5:N52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1189,47 +1259,47 @@
     <row r="5" spans="2:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
     </row>
     <row r="8" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
     </row>
     <row r="9" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
     </row>
     <row r="10" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
     </row>
     <row r="11" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
     </row>
     <row r="12" spans="2:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="15"/>
@@ -1239,23 +1309,23 @@
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="44"/>
+      <c r="G13" s="48"/>
       <c r="N13" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="2:14" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="45"/>
+      <c r="G14" s="49"/>
     </row>
     <row r="15" spans="2:14" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="8"/>
@@ -1282,12 +1352,12 @@
       </c>
     </row>
     <row r="17" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="49"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="53"/>
       <c r="F17" s="25"/>
       <c r="G17" s="26"/>
     </row>
@@ -1523,25 +1593,25 @@
       </c>
     </row>
     <row r="29" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="52"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="56"/>
       <c r="G29" s="32">
         <f>SUM(G18:G28)</f>
         <v>11643000</v>
       </c>
     </row>
     <row r="30" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="55"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="59"/>
       <c r="F30" s="27"/>
       <c r="G30" s="26"/>
     </row>
@@ -1587,7 +1657,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="33" spans="2:8" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2">
         <v>3</v>
       </c>
@@ -1608,7 +1678,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="34" spans="2:8" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
         <v>4</v>
       </c>
@@ -1629,7 +1699,7 @@
         <v>363000</v>
       </c>
     </row>
-    <row r="35" spans="2:8" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2">
         <v>5</v>
       </c>
@@ -1650,109 +1720,184 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="36" spans="2:8" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="50" t="s">
+    <row r="36" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="52"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="56"/>
       <c r="G36" s="33">
         <f>SUM(G31:G35)</f>
         <v>4763000</v>
       </c>
     </row>
-    <row r="37" spans="2:8" s="6" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-    </row>
-    <row r="38" spans="2:8" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="39" t="s">
+    <row r="37" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="60"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="62"/>
+      <c r="G37" s="63"/>
+    </row>
+    <row r="38" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="63"/>
+    </row>
+    <row r="39" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="65">
+        <v>1</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="66">
+        <v>1</v>
+      </c>
+      <c r="E39" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="27">
+        <v>750000</v>
+      </c>
+      <c r="G39" s="27">
+        <f>F39*D39</f>
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="65">
+        <v>2</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="66">
+        <v>1</v>
+      </c>
+      <c r="E40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" s="27">
+        <v>135000</v>
+      </c>
+      <c r="G40" s="26">
+        <f>F40*D40</f>
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="32">
+        <f>SUM(G39:H40)</f>
+        <v>885000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+    </row>
+    <row r="43" spans="2:7" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="29">
-        <f>G36+G29</f>
-        <v>16406000</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="19"/>
-    </row>
-    <row r="41" spans="2:8" s="21" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B41" s="42" t="s">
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="29">
+        <f>G29+G36+G41</f>
+        <v>17291000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="19"/>
+    </row>
+    <row r="46" spans="2:7" s="21" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B46" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="43" t="s">
+      <c r="C46" s="46"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G41" s="43"/>
-    </row>
-    <row r="45" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="59"/>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="37" t="s">
+      <c r="G46" s="47"/>
+    </row>
+    <row r="50" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="23"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="34" t="s">
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="23"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="23"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="B52:G52"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="F46:G46"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="7.874015748031496E-2" bottom="0.74803149606299213" header="0.59055118110236227" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="85" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>
